--- a/Homework/src/test/java/Book 2.xlsx
+++ b/Homework/src/test/java/Book 2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F322D445-6A52-4CF2-90D6-902BEED4C87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5D1E569-9D33-4F07-8CBA-CB25019623A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>email</t>
   </si>
@@ -39,28 +39,37 @@
     <t>password</t>
   </si>
   <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
     <t>nourbzour</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fail - Error: Please enter Email Address in a valid format. Error: Please enter Current Password.</t>
+  </si>
+  <si>
     <t>nourbzour65@gmail.com</t>
   </si>
   <si>
     <t>Noor123456</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fail - Email/Password you entered is not correct. Please try again.</t>
+  </si>
+  <si>
     <t>Eman@1282Bzoor</t>
   </si>
   <si>
-    <t>Fail - Error: Please enter Email Address in a valid format.</t>
+    <t xml:space="preserve"> Pass</t>
+  </si>
+  <si>
+    <t>Fail - Error: Please enter Email Address in a valid format. Error: Please enter Current Password.</t>
   </si>
   <si>
     <t>Fail - Email/Password you entered is not correct. Please try again.</t>
   </si>
   <si>
     <t>Pass</t>
-  </si>
-  <si>
-    <t>Fail - Error: Please enter Email Address in a valid format. Error: Please enter Current Password.</t>
   </si>
 </sst>
 </file>
@@ -460,42 +469,45 @@
     <col min="3" max="3" customWidth="true" width="101.85546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Homework/src/test/java/Book 2.xlsx
+++ b/Homework/src/test/java/Book 2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
   <si>
     <t>email</t>
   </si>
@@ -70,6 +70,17 @@
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail - Fail - Remember me on this device
+SIGN IN
+Forgot your password?</t>
+  </si>
+  <si>
+    <t>Fail - Pass</t>
+  </si>
+  <si>
+    <t>Fail - Fail - Email/Password you entered is not correct. Please try again.</t>
   </si>
 </sst>
 </file>
@@ -507,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
